--- a/quizzes/015_solid_geometry_assessment--quizzes.xlsx
+++ b/quizzes/015_solid_geometry_assessment--quizzes.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -663,7 +663,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>What is the surface area of the sphere?</t>
+          <t>Answer Five</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -782,7 +782,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Student Grade</t>
+          <t>Student Grade Two</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -828,7 +828,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>What is the volume of the sphere?</t>
+          <t>Answer Seven</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -874,7 +874,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>What is the surface area of the sphere?</t>
+          <t>Answer Eight</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -897,7 +897,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>What is the surface area of the rectangular prism?</t>
+          <t>Answer Nine</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -943,7 +943,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>What is the volume of the cylinder?</t>
+          <t>Answer Eleven</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -966,7 +966,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>What is the surface area of the cylinder?</t>
+          <t>Answer Twelve</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>What is the surface area of the rectangular prism?</t>
+          <t>Answer Fourteen</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1035,7 +1035,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>What is the volume of the sphere?</t>
+          <t>Answer Fifteen</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1058,7 +1058,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>What is the surface area of the sphere?</t>
+          <t>Answer Sixteen</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1081,7 +1081,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>What is the volume of the sphere?</t>
+          <t>Answer Seventeen</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1106,8 +1106,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1135,12 +1135,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Option 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1152,12 +1152,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Option 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1169,12 +1169,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'option_3'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Option 3'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Option 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1203,12 +1203,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Option 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1220,12 +1220,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'option_3'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Option 3'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1237,12 +1237,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Option 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1254,12 +1254,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Option 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1271,12 +1271,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'option_3'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Option 3'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1288,12 +1288,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Option 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1305,12 +1305,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Option 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1322,12 +1322,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'option_3'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Option 3'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1339,12 +1339,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Option 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1356,12 +1356,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Option 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1373,12 +1373,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'option_3'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Option 3'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1390,12 +1390,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'option_4'}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Option 4'}</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -1407,12 +1407,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Option 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1424,12 +1424,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Option 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1441,12 +1441,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'option_3'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Option 3'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1492,12 +1492,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Option 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1509,12 +1509,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Option 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Option 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1543,12 +1543,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Option 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1560,12 +1560,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'option_3'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Option 3'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1577,12 +1577,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Option 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1594,12 +1594,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Option 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1611,12 +1611,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'option_3'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Option 3'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1628,12 +1628,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'option_4'}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Option 4'}</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
